--- a/backtest_runs/20260410_193731/filter/ATRL/ATRL.xlsx
+++ b/backtest_runs/20260410_193731/filter/ATRL/ATRL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>102399.73</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>102399.73</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>103063.93</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>103063.93</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>103063.93</v>
@@ -1093,7 +1093,7 @@
         <v>-503.0699999999899</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>102560.86</v>
@@ -1185,7 +1185,7 @@
         <v>-2013.510000000001</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>101297.65</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>101297.65</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>101297.65</v>
@@ -1507,7 +1507,7 @@
         <v>-2250.899999999994</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>99046.75</v>
@@ -1553,7 +1553,7 @@
         <v>-1630.979999999999</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>97415.77</v>
@@ -1645,7 +1645,7 @@
         <v>-824.0999999999916</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>101683.87</v>
